--- a/data/trans_dic/P33_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P33_1_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño (tasa de respuesta: 98,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,06; 88,22</t>
+          <t>78,91; 88,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,25; 78,85</t>
+          <t>68,6; 79,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,5; 73,45</t>
+          <t>60,85; 72,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62,46; 74,63</t>
+          <t>62,88; 74,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,46; 88,64</t>
+          <t>79,07; 88,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,86; 70,14</t>
+          <t>57,92; 70,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,74; 69,86</t>
+          <t>57,54; 68,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,94; 69,39</t>
+          <t>59,94; 69,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>80,37; 87,06</t>
+          <t>80,35; 86,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64,49; 72,89</t>
+          <t>64,65; 72,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61,07; 69,07</t>
+          <t>60,98; 69,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,58; 71,11</t>
+          <t>63,22; 70,79</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72,55; 80,4</t>
+          <t>72,75; 80,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,73; 76,45</t>
+          <t>67,79; 76,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,44; 77,44</t>
+          <t>69,07; 77,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66,14; 77,28</t>
+          <t>66,26; 76,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,39; 70,25</t>
+          <t>61,38; 69,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,53; 69,27</t>
+          <t>60,26; 69,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,61; 67,52</t>
+          <t>58,91; 67,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>65,44; 72,74</t>
+          <t>65,32; 72,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,32; 73,83</t>
+          <t>67,83; 73,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65,25; 71,33</t>
+          <t>65,12; 71,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,97; 71,17</t>
+          <t>65,43; 71,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,18; 74,06</t>
+          <t>67,17; 73,69</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,5; 90,59</t>
+          <t>82,75; 90,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,6; 74,93</t>
+          <t>64,56; 75,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,3; 90,75</t>
+          <t>83,48; 90,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,54; 77,89</t>
+          <t>68,75; 78,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74,66; 83,85</t>
+          <t>74,91; 84,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,03; 72,91</t>
+          <t>61,73; 72,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,09; 82,59</t>
+          <t>73,87; 82,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63,81; 72,32</t>
+          <t>64,26; 72,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80,3; 86,07</t>
+          <t>80,33; 86,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64,88; 72,3</t>
+          <t>65,06; 72,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79,61; 85,68</t>
+          <t>79,48; 85,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,77; 73,99</t>
+          <t>67,98; 74,13</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,65; 90,16</t>
+          <t>83,05; 90,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,98; 73,14</t>
+          <t>63,03; 73,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,66; 70,49</t>
+          <t>60,8; 70,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67,24; 79,02</t>
+          <t>66,62; 78,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,26; 85,25</t>
+          <t>77,42; 85,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,7; 59,99</t>
+          <t>49,83; 60,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,92; 63,12</t>
+          <t>52,86; 63,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,29; 81,85</t>
+          <t>60,99; 80,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>81,2; 86,83</t>
+          <t>81,24; 86,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58,0; 65,37</t>
+          <t>57,93; 64,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58,36; 65,34</t>
+          <t>58,1; 65,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,85; 78,71</t>
+          <t>66,2; 78,97</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>68,47; 80,57</t>
+          <t>68,15; 80,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61,37; 74,48</t>
+          <t>62,0; 75,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,06; 95,17</t>
+          <t>88,24; 95,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,77; 71,25</t>
+          <t>59,42; 71,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>63,77; 76,61</t>
+          <t>63,74; 76,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,67; 67,07</t>
+          <t>52,96; 66,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,16; 94,73</t>
+          <t>87,03; 94,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,61; 59,65</t>
+          <t>50,66; 59,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67,99; 76,4</t>
+          <t>68,32; 76,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,74; 68,79</t>
+          <t>59,18; 68,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89,21; 94,43</t>
+          <t>88,84; 94,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>55,74; 63,52</t>
+          <t>56,3; 63,58</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>79,76; 88,14</t>
+          <t>79,17; 88,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,43; 80,32</t>
+          <t>69,72; 79,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,85; 84,68</t>
+          <t>74,72; 84,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72,22; 80,75</t>
+          <t>72,46; 80,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>71,16; 81,37</t>
+          <t>70,84; 80,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66,0; 76,68</t>
+          <t>66,02; 76,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,0; 75,3</t>
+          <t>62,84; 74,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,96; 69,21</t>
+          <t>60,27; 69,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76,58; 83,49</t>
+          <t>76,76; 83,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69,08; 76,83</t>
+          <t>69,52; 77,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70,54; 78,0</t>
+          <t>70,57; 78,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>67,96; 74,27</t>
+          <t>68,12; 74,49</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>81,02; 87,38</t>
+          <t>81,35; 87,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>75,17; 81,7</t>
+          <t>75,51; 82,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69,08; 76,49</t>
+          <t>69,39; 76,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63,91; 72,7</t>
+          <t>64,52; 73,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,31; 80,31</t>
+          <t>72,8; 79,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,39; 74,79</t>
+          <t>67,58; 74,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,19; 73,31</t>
+          <t>65,9; 73,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,36; 64,47</t>
+          <t>24,67; 64,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>78,25; 82,66</t>
+          <t>78,02; 82,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72,47; 77,18</t>
+          <t>72,34; 77,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68,8; 73,91</t>
+          <t>68,71; 73,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,86; 66,81</t>
+          <t>36,17; 66,97</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>74,01; 80,3</t>
+          <t>74,44; 80,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74,11; 80,38</t>
+          <t>74,17; 80,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78,23; 83,73</t>
+          <t>78,16; 83,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87,86; 96,46</t>
+          <t>87,67; 95,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>72,98; 79,19</t>
+          <t>72,84; 79,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,24; 76,9</t>
+          <t>70,33; 76,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,68; 82,62</t>
+          <t>76,28; 82,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>83,53; 88,04</t>
+          <t>83,75; 87,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>74,41; 78,82</t>
+          <t>74,48; 78,88</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73,27; 77,72</t>
+          <t>73,17; 77,68</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78,39; 82,55</t>
+          <t>78,44; 82,41</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>86,7; 93,2</t>
+          <t>86,57; 93,16</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>80,16; 82,8</t>
+          <t>79,98; 82,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72,57; 75,59</t>
+          <t>72,41; 75,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75,34; 78,3</t>
+          <t>75,35; 78,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74,57; 82,57</t>
+          <t>74,27; 82,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>74,51; 77,4</t>
+          <t>74,42; 77,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,95; 69,24</t>
+          <t>65,63; 69,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69,93; 73,14</t>
+          <t>69,9; 73,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>53,85; 70,67</t>
+          <t>53,22; 70,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>77,7; 79,69</t>
+          <t>77,61; 79,61</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69,55; 71,84</t>
+          <t>69,68; 71,95</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73,05; 75,15</t>
+          <t>72,94; 75,15</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>64,96; 74,31</t>
+          <t>64,36; 74,58</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño (tasa de respuesta: 98,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>212399; 236996</t>
+          <t>211997; 236636</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>200256; 231375</t>
+          <t>201282; 232380</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179682; 214591</t>
+          <t>177800; 212398</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>194533; 232419</t>
+          <t>195838; 232916</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>204976; 228650</t>
+          <t>203958; 228506</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>165634; 200775</t>
+          <t>165805; 201010</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>163671; 198047</t>
+          <t>163123; 195555</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>173617; 200990</t>
+          <t>173594; 200425</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>423236; 458482</t>
+          <t>423132; 457477</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>373852; 422557</t>
+          <t>374778; 420731</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>351565; 397624</t>
+          <t>351059; 398071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>382172; 427435</t>
+          <t>380013; 425499</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>357742; 396453</t>
+          <t>358723; 394779</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>340316; 384147</t>
+          <t>340616; 382092</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>349000; 389185</t>
+          <t>347126; 388001</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>279926; 327052</t>
+          <t>280408; 325410</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>308165; 352658</t>
+          <t>308115; 350292</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>317016; 362821</t>
+          <t>315613; 362562</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>306595; 353169</t>
+          <t>308138; 352301</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>289539; 321816</t>
+          <t>288976; 321396</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>679796; 734624</t>
+          <t>674932; 734757</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>669559; 731984</t>
+          <t>668299; 730566</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>666340; 729930</t>
+          <t>671110; 731636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>581524; 641057</t>
+          <t>581425; 637920</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>259053; 284440</t>
+          <t>259821; 285577</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>207407; 240547</t>
+          <t>207277; 241457</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>265349; 289084</t>
+          <t>265953; 289332</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>214931; 244254</t>
+          <t>215587; 246464</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>247459; 277919</t>
+          <t>248308; 278540</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>211539; 248624</t>
+          <t>210515; 246691</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>245820; 277760</t>
+          <t>248424; 277722</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>220589; 249984</t>
+          <t>222131; 251039</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>518305; 555510</t>
+          <t>518508; 555730</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>429532; 478692</t>
+          <t>430706; 478998</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>521355; 561124</t>
+          <t>520510; 559805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>446763; 487785</t>
+          <t>448155; 488707</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>288491; 314709</t>
+          <t>289878; 314899</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>235540; 273537</t>
+          <t>235716; 273510</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>223924; 260212</t>
+          <t>224455; 261723</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>206577; 242800</t>
+          <t>204675; 240862</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>286978; 316662</t>
+          <t>287588; 316464</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>192740; 232629</t>
+          <t>193246; 235015</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>202150; 241092</t>
+          <t>201919; 241605</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>280079; 374041</t>
+          <t>278715; 367960</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>585014; 625608</t>
+          <t>585352; 626545</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>441847; 497942</t>
+          <t>441257; 494714</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>438330; 490752</t>
+          <t>436389; 492174</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>503237; 601571</t>
+          <t>505951; 603489</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>139201; 163799</t>
+          <t>138556; 163062</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>130489; 158365</t>
+          <t>131825; 159737</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>186000; 201012</t>
+          <t>186391; 202026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>106829; 127361</t>
+          <t>106205; 127317</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>131805; 158337</t>
+          <t>131740; 158541</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>117381; 146671</t>
+          <t>115820; 145083</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>190514; 207074</t>
+          <t>190244; 207189</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>105433; 124261</t>
+          <t>105540; 123666</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>278741; 313242</t>
+          <t>280091; 314480</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>257684; 296724</t>
+          <t>255272; 294525</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>383429; 405883</t>
+          <t>381857; 404512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>215738; 245865</t>
+          <t>217912; 246099</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>214468; 236976</t>
+          <t>212866; 236948</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>190217; 220050</t>
+          <t>191029; 217443</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>196935; 222809</t>
+          <t>196611; 222179</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>194730; 217733</t>
+          <t>195366; 217449</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>196525; 224715</t>
+          <t>195633; 223502</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>184833; 214725</t>
+          <t>184877; 213509</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>174172; 204922</t>
+          <t>171026; 203275</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>153920; 177656</t>
+          <t>154725; 178523</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>417379; 455039</t>
+          <t>418345; 454256</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>382731; 425644</t>
+          <t>385169; 426625</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>377580; 417536</t>
+          <t>377726; 418810</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>357715; 390930</t>
+          <t>358570; 392087</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>490963; 529472</t>
+          <t>492980; 529321</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>496013; 539104</t>
+          <t>498279; 542101</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>450532; 498889</t>
+          <t>452585; 500156</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>398999; 453872</t>
+          <t>402778; 455736</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>465373; 509824</t>
+          <t>462149; 506839</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>466771; 518003</t>
+          <t>468072; 516561</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>456250; 505347</t>
+          <t>454279; 504693</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>197265; 544324</t>
+          <t>208317; 546017</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>970954; 1025585</t>
+          <t>968033; 1027350</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>980081; 1043860</t>
+          <t>978369; 1045800</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>922957; 991570</t>
+          <t>921821; 990277</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>541304; 981193</t>
+          <t>531127; 983527</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>537793; 583531</t>
+          <t>540919; 583917</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>575262; 623898</t>
+          <t>575726; 622140</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>609122; 651882</t>
+          <t>608511; 652810</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>815951; 895839</t>
+          <t>814189; 889794</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>566786; 614967</t>
+          <t>565650; 615970</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>575126; 629671</t>
+          <t>575865; 629636</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>632661; 681719</t>
+          <t>629364; 679922</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>596701; 628918</t>
+          <t>598248; 628514</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1118586; 1184821</t>
+          <t>1119711; 1185839</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1168604; 1239680</t>
+          <t>1167066; 1239015</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1257063; 1323839</t>
+          <t>1257997; 1321584</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1424489; 1531373</t>
+          <t>1422396; 1530725</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2588708; 2674029</t>
+          <t>2582930; 2674378</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2477335; 2580460</t>
+          <t>2471615; 2581173</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2552237; 2652505</t>
+          <t>2552675; 2658807</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2503236; 2771638</t>
+          <t>2493003; 2764034</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2501367; 2598566</t>
+          <t>2498276; 2596209</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2340558; 2457196</t>
+          <t>2329295; 2449801</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2468587; 2581803</t>
+          <t>2467351; 2578401</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1916101; 2514675</t>
+          <t>1893941; 2510660</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5118185; 5248700</t>
+          <t>5112156; 5243770</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4842118; 5001553</t>
+          <t>4851463; 5009745</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5053561; 5198847</t>
+          <t>5045986; 5198786</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4492493; 5138820</t>
+          <t>4450941; 5157772</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P33_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P33_1_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,91; 88,08</t>
+          <t>78,75; 87,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68,6; 79,19</t>
+          <t>68,46; 78,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,85; 72,7</t>
+          <t>60,1; 72,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62,88; 74,79</t>
+          <t>63,61; 74,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,07; 88,58</t>
+          <t>78,65; 88,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,92; 70,22</t>
+          <t>58,33; 69,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,54; 68,98</t>
+          <t>56,85; 68,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,94; 69,2</t>
+          <t>62,12; 70,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>80,35; 86,87</t>
+          <t>80,48; 87,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64,65; 72,58</t>
+          <t>65,0; 72,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60,98; 69,15</t>
+          <t>61,57; 69,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,22; 70,79</t>
+          <t>64,61; 71,28</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72,75; 80,06</t>
+          <t>72,62; 80,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,79; 76,05</t>
+          <t>67,82; 76,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,07; 77,2</t>
+          <t>69,43; 77,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66,26; 76,89</t>
+          <t>67,46; 77,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,38; 69,78</t>
+          <t>61,65; 70,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,26; 69,22</t>
+          <t>60,23; 69,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,91; 67,35</t>
+          <t>59,02; 67,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>65,32; 72,65</t>
+          <t>65,21; 72,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67,83; 73,84</t>
+          <t>68,19; 73,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65,12; 71,19</t>
+          <t>65,47; 71,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65,43; 71,33</t>
+          <t>65,05; 71,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,17; 73,69</t>
+          <t>67,55; 73,94</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,75; 90,95</t>
+          <t>82,7; 90,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,56; 75,21</t>
+          <t>64,47; 74,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,48; 90,82</t>
+          <t>83,2; 90,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,75; 78,59</t>
+          <t>67,89; 77,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74,91; 84,03</t>
+          <t>74,77; 83,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,73; 72,34</t>
+          <t>62,65; 72,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,87; 82,58</t>
+          <t>73,93; 82,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,26; 72,62</t>
+          <t>64,27; 72,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80,33; 86,1</t>
+          <t>80,31; 85,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65,06; 72,35</t>
+          <t>65,19; 72,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79,48; 85,48</t>
+          <t>79,41; 85,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,98; 74,13</t>
+          <t>67,24; 73,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,05; 90,22</t>
+          <t>82,86; 90,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,03; 73,13</t>
+          <t>62,88; 72,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,8; 70,9</t>
+          <t>60,54; 70,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66,62; 78,39</t>
+          <t>66,05; 77,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,42; 85,2</t>
+          <t>77,69; 85,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,83; 60,61</t>
+          <t>50,24; 61,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,86; 63,25</t>
+          <t>52,76; 63,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>60,99; 80,52</t>
+          <t>56,72; 65,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>81,24; 86,96</t>
+          <t>81,28; 86,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,93; 64,94</t>
+          <t>57,88; 65,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58,1; 65,53</t>
+          <t>58,02; 65,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,2; 78,97</t>
+          <t>62,59; 70,18</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>61,02%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>68,15; 80,2</t>
+          <t>68,13; 80,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,0; 75,13</t>
+          <t>62,11; 75,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,24; 95,65</t>
+          <t>87,75; 95,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,42; 71,23</t>
+          <t>61,72; 72,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>63,74; 76,71</t>
+          <t>63,43; 76,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,96; 66,34</t>
+          <t>53,22; 66,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,03; 94,79</t>
+          <t>87,39; 94,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>50,66; 59,36</t>
+          <t>51,18; 60,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68,32; 76,71</t>
+          <t>68,12; 77,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,18; 68,28</t>
+          <t>59,1; 68,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88,84; 94,11</t>
+          <t>88,85; 94,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>56,3; 63,58</t>
+          <t>57,26; 64,36</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>79,17; 88,13</t>
+          <t>79,29; 88,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69,72; 79,36</t>
+          <t>69,11; 79,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,72; 84,44</t>
+          <t>74,81; 84,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72,46; 80,65</t>
+          <t>71,69; 80,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70,84; 80,93</t>
+          <t>70,81; 80,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66,02; 76,24</t>
+          <t>66,47; 76,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,84; 74,69</t>
+          <t>63,65; 74,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60,27; 69,54</t>
+          <t>60,0; 68,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76,76; 83,34</t>
+          <t>76,34; 83,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69,52; 77,01</t>
+          <t>69,31; 76,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70,57; 78,24</t>
+          <t>70,31; 78,36</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>68,12; 74,49</t>
+          <t>67,1; 73,67</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>66,54%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>81,35; 87,35</t>
+          <t>81,14; 87,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>75,51; 82,15</t>
+          <t>74,99; 81,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69,39; 76,69</t>
+          <t>69,41; 76,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64,52; 73,0</t>
+          <t>66,22; 73,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,8; 79,84</t>
+          <t>73,01; 79,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,58; 74,58</t>
+          <t>67,2; 74,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,9; 73,21</t>
+          <t>65,85; 73,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24,67; 64,67</t>
+          <t>60,13; 66,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>78,02; 82,8</t>
+          <t>78,19; 82,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72,34; 77,33</t>
+          <t>72,21; 77,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68,71; 73,82</t>
+          <t>68,95; 73,88</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,17; 66,97</t>
+          <t>64,0; 69,16</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>87,29%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>74,44; 80,35</t>
+          <t>73,99; 80,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74,17; 80,15</t>
+          <t>73,66; 80,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78,16; 83,85</t>
+          <t>77,95; 83,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87,67; 95,81</t>
+          <t>86,57; 91,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>72,84; 79,32</t>
+          <t>72,77; 79,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,33; 76,9</t>
+          <t>70,29; 76,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,28; 82,41</t>
+          <t>76,74; 82,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>83,75; 87,99</t>
+          <t>83,3; 87,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>74,48; 78,88</t>
+          <t>74,34; 78,78</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73,17; 77,68</t>
+          <t>73,22; 77,46</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78,44; 82,41</t>
+          <t>78,38; 82,51</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>86,57; 93,16</t>
+          <t>85,76; 88,81</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>79,98; 82,81</t>
+          <t>79,88; 82,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72,41; 75,62</t>
+          <t>72,61; 75,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75,35; 78,49</t>
+          <t>75,25; 78,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74,27; 82,34</t>
+          <t>73,92; 77,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>74,42; 77,33</t>
+          <t>74,35; 77,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,63; 69,03</t>
+          <t>65,73; 69,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69,9; 73,04</t>
+          <t>69,91; 73,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>53,22; 70,55</t>
+          <t>67,72; 70,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>77,61; 79,61</t>
+          <t>77,7; 79,68</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69,68; 71,95</t>
+          <t>69,55; 71,73</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72,94; 75,15</t>
+          <t>72,96; 75,19</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>64,36; 74,58</t>
+          <t>71,3; 73,35</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214561</t>
+          <t>220119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>188243</t>
+          <t>209722</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>402803</t>
+          <t>429841</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>211997; 236636</t>
+          <t>211560; 235882</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>201282; 232380</t>
+          <t>200876; 231406</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>177800; 212398</t>
+          <t>175607; 210764</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>195838; 232916</t>
+          <t>202817; 235934</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>203958; 228506</t>
+          <t>202889; 227585</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>165805; 201010</t>
+          <t>166982; 200135</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>163123; 195555</t>
+          <t>161171; 194358</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>173594; 200425</t>
+          <t>196343; 223227</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>423132; 457477</t>
+          <t>423833; 459465</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>374778; 420731</t>
+          <t>376794; 422855</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>351059; 398071</t>
+          <t>354430; 401211</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>380013; 425499</t>
+          <t>410243; 452555</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>305594</t>
+          <t>315235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>305678</t>
+          <t>323459</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>611272</t>
+          <t>638694</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>358723; 394779</t>
+          <t>358078; 395383</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>340616; 382092</t>
+          <t>340751; 384638</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>347126; 388001</t>
+          <t>348955; 389215</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>280408; 325410</t>
+          <t>293533; 336898</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>308115; 350292</t>
+          <t>309501; 351764</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>315613; 362562</t>
+          <t>315481; 361717</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>308138; 352301</t>
+          <t>308735; 353051</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>288976; 321396</t>
+          <t>306292; 341653</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>674932; 734757</t>
+          <t>678585; 734866</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>668299; 730566</t>
+          <t>671819; 733697</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>671110; 731636</t>
+          <t>667233; 728540</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>581425; 637920</t>
+          <t>611208; 668987</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>231649</t>
+          <t>228775</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>236741</t>
+          <t>240006</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>468390</t>
+          <t>468781</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>259821; 285577</t>
+          <t>259660; 285666</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>207277; 241457</t>
+          <t>206972; 240560</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>265953; 289332</t>
+          <t>265062; 287844</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215587; 246464</t>
+          <t>212902; 243544</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>248308; 278540</t>
+          <t>247849; 277827</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>210515; 246691</t>
+          <t>213662; 248171</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>248424; 277722</t>
+          <t>248648; 278427</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>222131; 251039</t>
+          <t>226392; 254343</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>518508; 555730</t>
+          <t>518383; 554616</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>430706; 478998</t>
+          <t>431586; 480530</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>520510; 559805</t>
+          <t>520052; 557222</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>448155; 488707</t>
+          <t>447723; 489507</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>225655</t>
+          <t>265262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>317580</t>
+          <t>246009</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>543235</t>
+          <t>511270</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>289878; 314899</t>
+          <t>289233; 315649</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>235716; 273510</t>
+          <t>235173; 272444</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>224455; 261723</t>
+          <t>223473; 260883</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>204675; 240862</t>
+          <t>242244; 284601</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>287588; 316464</t>
+          <t>288576; 317975</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>193246; 235015</t>
+          <t>194834; 237420</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>201919; 241605</t>
+          <t>201512; 241780</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>278715; 367960</t>
+          <t>227915; 264159</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>585352; 626545</t>
+          <t>585649; 624965</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>441257; 494714</t>
+          <t>440936; 496361</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>436389; 492174</t>
+          <t>435765; 491086</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>505951; 603489</t>
+          <t>481088; 539429</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117053</t>
+          <t>137830</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>114251</t>
+          <t>126092</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>231304</t>
+          <t>263922</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>138556; 163062</t>
+          <t>138504; 163203</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>131825; 159737</t>
+          <t>132066; 159632</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>186391; 202026</t>
+          <t>185351; 201674</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>106205; 127317</t>
+          <t>126944; 149004</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>131740; 158541</t>
+          <t>131096; 158850</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>115820; 145083</t>
+          <t>116393; 144778</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>190244; 207189</t>
+          <t>191019; 207587</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>105540; 123666</t>
+          <t>116115; 137218</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>280091; 314480</t>
+          <t>279272; 315739</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>255272; 294525</t>
+          <t>254889; 296750</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>381857; 404512</t>
+          <t>381866; 405451</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>217912; 246099</t>
+          <t>247681; 278403</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>207514</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>167077</t>
+          <t>170750</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>374289</t>
+          <t>378264</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>212866; 236948</t>
+          <t>213184; 236934</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>191029; 217443</t>
+          <t>189345; 218122</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>196611; 222179</t>
+          <t>196831; 221900</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>195366; 217449</t>
+          <t>194061; 217766</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>195633; 223502</t>
+          <t>195542; 223338</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>184877; 213509</t>
+          <t>186134; 215315</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>171026; 203275</t>
+          <t>173210; 202244</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>154725; 178523</t>
+          <t>158021; 181580</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>418345; 454256</t>
+          <t>416090; 454247</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>385169; 426625</t>
+          <t>384000; 425922</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>377726; 418810</t>
+          <t>376330; 419452</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>358570; 392087</t>
+          <t>358355; 393456</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>430171</t>
+          <t>503739</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>404265</t>
+          <t>483561</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>834436</t>
+          <t>987301</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>492980; 529321</t>
+          <t>491661; 529488</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>498279; 542101</t>
+          <t>494861; 539726</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>452585; 500156</t>
+          <t>452658; 500334</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>402778; 455736</t>
+          <t>476573; 530339</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>462149; 506839</t>
+          <t>463490; 504926</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>468072; 516561</t>
+          <t>465440; 517543</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>454279; 504693</t>
+          <t>453903; 503504</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>208317; 546017</t>
+          <t>459521; 509720</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>968033; 1027350</t>
+          <t>970208; 1027901</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>978369; 1045800</t>
+          <t>976592; 1042523</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>921821; 990277</t>
+          <t>924952; 991086</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>531127; 983527</t>
+          <t>949739; 1026251</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>850283</t>
+          <t>709765</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>613619</t>
+          <t>710930</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1463903</t>
+          <t>1420695</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>540919; 583917</t>
+          <t>537641; 583412</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>575726; 622140</t>
+          <t>571756; 622390</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>608511; 652810</t>
+          <t>606925; 652091</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>814189; 889794</t>
+          <t>690928; 726290</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>565650; 615970</t>
+          <t>565094; 615181</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>575865; 629636</t>
+          <t>575559; 629476</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>629364; 679922</t>
+          <t>633145; 681683</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>598248; 628514</t>
+          <t>690915; 728089</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1119711; 1185839</t>
+          <t>1117533; 1184224</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1167066; 1239015</t>
+          <t>1167790; 1235524</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1257997; 1321584</t>
+          <t>1256937; 1323160</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1422396; 1530725</t>
+          <t>1395648; 1445370</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2582177</t>
+          <t>2588239</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2347455</t>
+          <t>2510528</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4929632</t>
+          <t>5098767</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2582930; 2674378</t>
+          <t>2579842; 2675558</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2471615; 2581173</t>
+          <t>2478624; 2587028</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2552675; 2658807</t>
+          <t>2549311; 2652481</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2493003; 2764034</t>
+          <t>2534456; 2641203</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2498276; 2596209</t>
+          <t>2496057; 2595772</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2329295; 2449801</t>
+          <t>2332575; 2454347</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2467351; 2578401</t>
+          <t>2467735; 2577470</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1893941; 2510660</t>
+          <t>2453912; 2557005</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5112156; 5243770</t>
+          <t>5117800; 5248057</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4851463; 5009745</t>
+          <t>4842440; 4994265</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5045986; 5198786</t>
+          <t>5046798; 5201128</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4450941; 5157772</t>
+          <t>5028185; 5172690</t>
         </is>
       </c>
     </row>
